--- a/data_files/protein/PBDB_Proteins_Master.xlsx
+++ b/data_files/protein/PBDB_Proteins_Master.xlsx
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Peroxidase</t>
+          <t>Oxidoreductase</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
